--- a/rapport/data/benchmarks-results.xlsx
+++ b/rapport/data/benchmarks-results.xlsx
@@ -8,24 +8,39 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jorda\OneDrive\Documents\A4 Fise Info\ADS\cachebench\rapport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0EB203F-5BF7-411D-BC2A-A7195F3249F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C77BEAA-4BEE-4F49-9F5A-76E3A9B91FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1440" windowWidth="14400" windowHeight="7282" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10276" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet name="feuille1" sheetId="1" r:id="rId1"/>
+    <sheet name="Graphiques" sheetId="4" r:id="rId2"/>
+    <sheet name="Gains calculés" sheetId="2" r:id="rId3"/>
+    <sheet name="Données brute" sheetId="3" r:id="rId4"/>
+    <sheet name="Matrice décision" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="69">
   <si>
     <t>Stratégie</t>
   </si>
@@ -74,11 +89,173 @@
   <si>
     <t>?</t>
   </si>
+  <si>
+    <t>Métrique</t>
+  </si>
+  <si>
+    <t>Baseline</t>
+  </si>
+  <si>
+    <t>Caffeine</t>
+  </si>
+  <si>
+    <t>Redis</t>
+  </si>
+  <si>
+    <t>Nginx</t>
+  </si>
+  <si>
+    <t>Latence avg (ms)</t>
+  </si>
+  <si>
+    <t>Latence p50 (ms)</t>
+  </si>
+  <si>
+    <t>Latence p90 (ms)</t>
+  </si>
+  <si>
+    <t>Latence p95 (ms)</t>
+  </si>
+  <si>
+    <t>Latence max (ms)</t>
+  </si>
+  <si>
+    <t>Gain Caffeine (%)</t>
+  </si>
+  <si>
+    <t>Latence avg</t>
+  </si>
+  <si>
+    <t>Latence p50</t>
+  </si>
+  <si>
+    <t>Latence p90</t>
+  </si>
+  <si>
+    <t>Latence p95</t>
+  </si>
+  <si>
+    <t>Critère</t>
+  </si>
+  <si>
+    <t>Sans cache</t>
+  </si>
+  <si>
+    <t>Latence d'accès cache</t>
+  </si>
+  <si>
+    <t>&lt; 1 ms</t>
+  </si>
+  <si>
+    <t>1-3 ms</t>
+  </si>
+  <si>
+    <t>&lt; 0,5 ms</t>
+  </si>
+  <si>
+    <t>Complexité d'intégration</t>
+  </si>
+  <si>
+    <t>Aucune</t>
+  </si>
+  <si>
+    <t>Faible</t>
+  </si>
+  <si>
+    <t>Moyenne</t>
+  </si>
+  <si>
+    <t>Élevée</t>
+  </si>
+  <si>
+    <t>Coût infrastructure</t>
+  </si>
+  <si>
+    <t>Minimal</t>
+  </si>
+  <si>
+    <t>Moyen</t>
+  </si>
+  <si>
+    <t>Scalabilité horizontale</t>
+  </si>
+  <si>
+    <t>Bonne</t>
+  </si>
+  <si>
+    <t>Limitée</t>
+  </si>
+  <si>
+    <t>Excellente</t>
+  </si>
+  <si>
+    <t>Cohérence des données</t>
+  </si>
+  <si>
+    <t>Forte</t>
+  </si>
+  <si>
+    <t>Risque stale</t>
+  </si>
+  <si>
+    <t>Configurable</t>
+  </si>
+  <si>
+    <t>Granularité de contrôle</t>
+  </si>
+  <si>
+    <t>Fine</t>
+  </si>
+  <si>
+    <t>Grossière</t>
+  </si>
+  <si>
+    <t>Cacheabilité</t>
+  </si>
+  <si>
+    <t>Toute méthode</t>
+  </si>
+  <si>
+    <t>GET idempotent</t>
+  </si>
+  <si>
+    <t>Maturité Spring Boot</t>
+  </si>
+  <si>
+    <t>Native</t>
+  </si>
+  <si>
+    <t>Externe</t>
+  </si>
+  <si>
+    <t>Réversibilité</t>
+  </si>
+  <si>
+    <t>Pondération</t>
+  </si>
+  <si>
+    <t>Gain de latence attendu</t>
+  </si>
+  <si>
+    <t>Simplicité Spring</t>
+  </si>
+  <si>
+    <t>Adéquation mono-instance</t>
+  </si>
+  <si>
+    <t>Maturité écosystème</t>
+  </si>
+  <si>
+    <t>TOTAL pondéré /5</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -116,17 +293,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF9C27B0"/>
+      <color rgb="FF5A7B9A"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -136,6 +320,5634 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="fr-MC"/>
+              <a:t>Comparaison des latences : Baseline vs Caffeine</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx2"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Données brute'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Baseline</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx2">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Données brute'!$A$2:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>Latence avg (ms)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Latence p50 (ms)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Latence p90 (ms)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Latence p95 (ms)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Latence max (ms)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Débit (req/s)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Hit ratio (%)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Erreurs (%)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Données brute'!$B$2:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>29.3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>28.45</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>36.03</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>37.81</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>151.68</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>74.06</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3402-49C5-B82D-8E22DF1F9391}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Données brute'!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Caffeine</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent2">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent2">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx2">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Données brute'!$A$2:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>Latence avg (ms)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Latence p50 (ms)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Latence p90 (ms)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Latence p95 (ms)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Latence max (ms)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Débit (req/s)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Hit ratio (%)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Erreurs (%)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Données brute'!$C$2:$C$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1.22</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.02</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.77</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.11</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>84.43</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>78.08</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>99.8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-3402-49C5-B82D-8E22DF1F9391}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="100"/>
+        <c:overlap val="-24"/>
+        <c:axId val="1626286367"/>
+        <c:axId val="1626288287"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1626286367"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="fr-FR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1626288287"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1626288287"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="fr-MC"/>
+                  <a:t>latence (ms)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="fr-FR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1626286367"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx2"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx2">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="fr-MC" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>Gain de performance Caffeine vs Baseline</a:t>
+            </a:r>
+            <a:endParaRPr lang="fr-MC"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Gains calculés'!$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Latence p95</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Gains calculés'!$B$1:$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Gain Caffeine (%)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>95,8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>96,4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>95,1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Gains calculés'!$B$5</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>94.4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-98D6-413B-AAD0-A6DC5A630BDE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1089720943"/>
+        <c:axId val="1543874319"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1089720943"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1543874319"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1543874319"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1089720943"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="fr-MC" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>Comparaison des latences : Baseline vs Caffeine</a:t>
+            </a:r>
+            <a:endParaRPr lang="fr-MC"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Données brute'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Baseline</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Données brute'!$A$2:$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Latence avg (ms)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Latence p50 (ms)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Latence p90 (ms)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Latence p95 (ms)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Données brute'!$B$2:$B$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>29.3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>28.45</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>36.03</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>37.81</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B3DC-436F-AE77-28C0D53E0357}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Données brute'!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Caffeine</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Données brute'!$A$2:$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Latence avg (ms)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Latence p50 (ms)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Latence p90 (ms)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Latence p95 (ms)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Données brute'!$C$2:$C$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1.22</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.02</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.77</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.11</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-B3DC-436F-AE77-28C0D53E0357}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1746869743"/>
+        <c:axId val="1746866383"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1746869743"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="fr-MC"/>
+                  <a:t>Métriques</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.4720126859142606"/>
+              <c:y val="0.77277704870224551"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="fr-FR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1746866383"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1746866383"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="fr-MC" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+                  <a:t>Latence (ms)</a:t>
+                </a:r>
+                <a:endParaRPr lang="fr-MC"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="fr-FR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1746869743"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="fr-MC" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>Gain de performance Caffeine vs Baseline</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Gains calculés'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Gain Caffeine (%)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="00B050"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Gains calculés'!$A$2:$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Latence avg</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Latence p50</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Latence p90</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Latence p95</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Gains calculés'!$B$2:$B$5</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>95.8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>96.4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>95.1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>94.4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-05C9-469F-8DB2-1C68437A98C0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="1713774127"/>
+        <c:axId val="1713776527"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1713774127"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="fr-MC"/>
+                  <a:t>Métriques</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="fr-FR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1713776527"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1713776527"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="100"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="fr-MC" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+                  <a:t>Gain (%)</a:t>
+                </a:r>
+                <a:endParaRPr lang="fr-MC"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="fr-FR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1713774127"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="fr-MC" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>Débit (requêtes par seconde)</a:t>
+            </a:r>
+            <a:endParaRPr lang="fr-MC"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Données brute'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Baseline</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Données brute'!$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Débit (req/s)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Données brute'!$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>74.06</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4AC7-432A-8BA1-5E8EDC681654}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Données brute'!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Caffeine</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="fr-FR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Données brute'!$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Débit (req/s)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Données brute'!$C$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>78.08</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-4AC7-432A-8BA1-5E8EDC681654}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1711305663"/>
+        <c:axId val="1711304703"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1711305663"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1711304703"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1711304703"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="100"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="fr-MC" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+                  <a:t>req/s</a:t>
+                </a:r>
+                <a:endParaRPr lang="fr-MC"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="fr-FR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1711305663"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="207">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk2">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700">
+        <a:solidFill>
+          <a:schemeClr val="lt2"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>659605</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>659605</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Graphique 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7238EE2F-0610-017E-EFD0-EB712ABF058A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>45243</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>45243</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Graphique 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4EF8A7C4-B901-6C30-527F-CBC69E727CFA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>45243</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>45243</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Graphique 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0583E777-199E-9C7E-D286-58BC2F91C88B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1459705</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>14288</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>302417</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>42863</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Graphique 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B0ACBE0-2214-4B17-9CB6-9C61CED9740F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>659605</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>659605</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Graphique 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{672F7728-8772-443B-812C-5099B544BEFB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4A544063-DDD5-4002-A8AD-3988444D8870}" name="Tableau1" displayName="Tableau1" ref="A1:E9" totalsRowShown="0">
+  <autoFilter ref="A1:E9" xr:uid="{4A544063-DDD5-4002-A8AD-3988444D8870}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{66442F32-622E-4FEF-8C26-612EB8ABFF57}" name="Métrique"/>
+    <tableColumn id="2" xr3:uid="{FFB5BBF9-85AA-45C1-95A8-1CCBF6493281}" name="Baseline"/>
+    <tableColumn id="3" xr3:uid="{152136B8-182B-4044-A68B-19212CE40817}" name="Caffeine"/>
+    <tableColumn id="4" xr3:uid="{F7BAB9A8-9D3D-4BFB-92F1-D181F1B0CCAE}" name="Redis"/>
+    <tableColumn id="5" xr3:uid="{178BFC63-7A85-4611-9F42-D249430CDE11}" name="Nginx"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C933529C-01F5-4EA3-BB88-AFD37C8BA431}" name="Tableau2" displayName="Tableau2" ref="A1:E10" totalsRowShown="0">
+  <autoFilter ref="A1:E10" xr:uid="{C933529C-01F5-4EA3-BB88-AFD37C8BA431}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{06EC4E83-2194-4E89-AAD8-048E1F3CD4A4}" name="Critère"/>
+    <tableColumn id="2" xr3:uid="{A0A2A501-69CA-41B7-AAFC-B6B3F3771AFF}" name="Sans cache"/>
+    <tableColumn id="3" xr3:uid="{F935E5BF-7828-41DA-9799-EB0107F6B385}" name="Caffeine"/>
+    <tableColumn id="4" xr3:uid="{D8E13C50-56DC-4CD1-A006-74634C6FD777}" name="Redis"/>
+    <tableColumn id="5" xr3:uid="{F0467A45-183A-433B-9FEA-56ABDB26B7E2}" name="Nginx"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A1C8F2A3-22E4-4275-9C8A-2D17C4AEC812}" name="Tableau3" displayName="Tableau3" ref="A13:F20" totalsRowShown="0">
+  <autoFilter ref="A13:F20" xr:uid="{A1C8F2A3-22E4-4275-9C8A-2D17C4AEC812}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{E710D523-34F0-42D8-8A4D-9DC2FEC6A2B3}" name="Critère"/>
+    <tableColumn id="2" xr3:uid="{8EE93EAC-CBB3-439F-8D37-B497815F3CE1}" name="Pondération"/>
+    <tableColumn id="3" xr3:uid="{FE366B99-660D-4968-B5AC-49E0259B5604}" name="Sans cache"/>
+    <tableColumn id="4" xr3:uid="{9B8E7C6D-BC88-4F08-80E8-710CB407B82A}" name="Caffeine"/>
+    <tableColumn id="5" xr3:uid="{6B286BB2-19A2-472B-8695-0215558E9B18}" name="Redis"/>
+    <tableColumn id="6" xr3:uid="{1ECEB9B3-9220-4DF4-B4F8-CE9AFA620F75}" name="Nginx"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -404,7 +6216,7 @@
   <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -552,4 +6364,573 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86D1FEB0-C741-4207-9DFA-6C92878D482C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25D1AAFD-0161-4492-B39E-E006E40D5C0F}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="69.53125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="2">
+        <v>95.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="2">
+        <v>96.4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="2">
+        <v>95.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="2">
+        <v>94.4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF4FED6F-AE8F-4869-A528-218EEA734751}">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="23.3984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2">
+        <v>29.3</v>
+      </c>
+      <c r="C2">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3">
+        <v>28.45</v>
+      </c>
+      <c r="C3">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4">
+        <v>36.03</v>
+      </c>
+      <c r="C4">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5">
+        <v>37.81</v>
+      </c>
+      <c r="C5">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6">
+        <v>151.68</v>
+      </c>
+      <c r="C6">
+        <v>84.43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>74.06</v>
+      </c>
+      <c r="C7">
+        <v>78.08</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>99.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42D8447D-0A7F-402D-92A2-55CF976AD2BD}">
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="12.265625" customWidth="1"/>
+    <col min="3" max="3" width="11.06640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14">
+        <v>30</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>5</v>
+      </c>
+      <c r="E14">
+        <v>4</v>
+      </c>
+      <c r="F14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15">
+        <v>20</v>
+      </c>
+      <c r="C15">
+        <v>5</v>
+      </c>
+      <c r="D15">
+        <v>5</v>
+      </c>
+      <c r="E15">
+        <v>3</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16">
+        <v>15</v>
+      </c>
+      <c r="C16">
+        <v>3</v>
+      </c>
+      <c r="D16">
+        <v>5</v>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
+      <c r="F16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17">
+        <v>15</v>
+      </c>
+      <c r="C17">
+        <v>5</v>
+      </c>
+      <c r="D17">
+        <v>5</v>
+      </c>
+      <c r="E17">
+        <v>3</v>
+      </c>
+      <c r="F17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18">
+        <v>10</v>
+      </c>
+      <c r="C18">
+        <v>5</v>
+      </c>
+      <c r="D18">
+        <v>5</v>
+      </c>
+      <c r="E18">
+        <v>4</v>
+      </c>
+      <c r="F18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19">
+        <v>10</v>
+      </c>
+      <c r="C19">
+        <v>5</v>
+      </c>
+      <c r="D19">
+        <v>5</v>
+      </c>
+      <c r="E19">
+        <v>3</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20">
+        <f>SUMPRODUCT($B$14:$B$19,C14:C19)/SUM($B$14:$B$19)</f>
+        <v>3.5</v>
+      </c>
+      <c r="D20">
+        <f>SUMPRODUCT($B$14:$B$19,D14:D19)/SUM($B$14:$B$19)</f>
+        <v>5</v>
+      </c>
+      <c r="E20">
+        <f>SUMPRODUCT($B$14:$B$19,E14:E19)/SUM($B$14:$B$19)</f>
+        <v>3.4</v>
+      </c>
+      <c r="F20">
+        <f>SUMPRODUCT($B$14:$B$19,F14:F19)/SUM($B$14:$B$19)</f>
+        <v>3.45</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="C20:F20">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{61190FEF-6B45-4603-B415-FC7257F80687}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="2">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+  </tableParts>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{61190FEF-6B45-4603-B415-FC7257F80687}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>C20:F20</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
 </file>